--- a/utils/po_templates/po_template.xlsx
+++ b/utils/po_templates/po_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbolanos\Desktop\projects\cps-tool\utils\po_templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{149D4FF2-B778-47D6-B44C-E80F59AD32F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2DA0B71-ED23-42A0-8A63-CE9ACF51D50A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -142,7 +142,7 @@
     <numFmt numFmtId="167" formatCode="_([$€-2]\ * #,##0.00_);_([$€-2]\ * \(#,##0.00\);_([$€-2]\ * &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="168" formatCode="_-[$€-2]\ * #,##0.00_-;\-[$€-2]\ * #,##0.00_-;_-[$€-2]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -235,11 +235,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -614,7 +609,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -703,12 +698,6 @@
     <xf numFmtId="44" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -784,118 +773,118 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1307,12 +1296,12 @@
       <c r="H1" s="6"/>
       <c r="I1" s="6"/>
       <c r="J1" s="6"/>
-      <c r="K1" s="41" t="s">
+      <c r="K1" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
+      <c r="L1" s="39"/>
+      <c r="M1" s="39"/>
+      <c r="N1" s="39"/>
     </row>
     <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E2" s="6"/>
@@ -1321,10 +1310,10 @@
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
       <c r="J2" s="6"/>
-      <c r="K2" s="41"/>
-      <c r="L2" s="41"/>
-      <c r="M2" s="41"/>
-      <c r="N2" s="41"/>
+      <c r="K2" s="39"/>
+      <c r="L2" s="39"/>
+      <c r="M2" s="39"/>
+      <c r="N2" s="39"/>
     </row>
     <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E3" s="6"/>
@@ -1340,88 +1329,88 @@
       <c r="O3" s="6"/>
     </row>
     <row r="4" spans="1:15" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="K4" s="52" t="s">
+      <c r="K4" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="L4" s="42"/>
-      <c r="M4" s="42"/>
-      <c r="N4" s="42"/>
+      <c r="L4" s="40"/>
+      <c r="M4" s="40"/>
+      <c r="N4" s="40"/>
     </row>
     <row r="5" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="56" t="s">
+      <c r="B5" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="56"/>
+      <c r="C5" s="54"/>
       <c r="D5" s="20"/>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
       <c r="I5" s="10"/>
-      <c r="K5" s="51"/>
-      <c r="L5" s="43"/>
-      <c r="M5" s="43"/>
-      <c r="N5" s="43"/>
+      <c r="K5" s="49"/>
+      <c r="L5" s="41"/>
+      <c r="M5" s="41"/>
+      <c r="N5" s="41"/>
     </row>
     <row r="6" spans="1:15" s="1" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="53"/>
-      <c r="C6" s="53"/>
+      <c r="B6" s="51"/>
+      <c r="C6" s="51"/>
       <c r="D6" s="29"/>
       <c r="E6" s="30"/>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
       <c r="H6" s="7"/>
       <c r="I6" s="4"/>
-      <c r="K6" s="50" t="s">
+      <c r="K6" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="L6" s="57"/>
-      <c r="M6" s="57"/>
-      <c r="N6" s="57"/>
+      <c r="L6" s="55"/>
+      <c r="M6" s="55"/>
+      <c r="N6" s="55"/>
     </row>
     <row r="7" spans="1:15" s="1" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="54"/>
-      <c r="C7" s="54"/>
+      <c r="B7" s="52"/>
+      <c r="C7" s="52"/>
       <c r="D7" s="29"/>
       <c r="E7" s="30"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
       <c r="I7" s="4"/>
-      <c r="K7" s="51"/>
-      <c r="L7" s="43"/>
-      <c r="M7" s="43"/>
-      <c r="N7" s="43"/>
+      <c r="K7" s="49"/>
+      <c r="L7" s="41"/>
+      <c r="M7" s="41"/>
+      <c r="N7" s="41"/>
     </row>
     <row r="8" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="54"/>
-      <c r="C8" s="54"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="52"/>
       <c r="D8" s="29"/>
       <c r="E8" s="30"/>
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
       <c r="I8" s="4"/>
-      <c r="K8" s="58" t="s">
+      <c r="K8" s="56" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="57"/>
-      <c r="M8" s="57"/>
-      <c r="N8" s="57"/>
+      <c r="L8" s="55"/>
+      <c r="M8" s="55"/>
+      <c r="N8" s="55"/>
     </row>
     <row r="9" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="54"/>
-      <c r="C9" s="54"/>
+      <c r="B9" s="52"/>
+      <c r="C9" s="52"/>
       <c r="D9" s="29"/>
       <c r="E9" s="30"/>
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
       <c r="I9" s="4"/>
-      <c r="K9" s="58"/>
-      <c r="L9" s="43"/>
-      <c r="M9" s="43"/>
-      <c r="N9" s="43"/>
+      <c r="K9" s="56"/>
+      <c r="L9" s="41"/>
+      <c r="M9" s="41"/>
+      <c r="N9" s="41"/>
     </row>
     <row r="10" spans="1:15" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="7"/>
@@ -1452,76 +1441,76 @@
       <c r="B12" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="61" t="s">
+      <c r="C12" s="57" t="s">
         <v>2</v>
       </c>
-      <c r="D12" s="62"/>
-      <c r="E12" s="62"/>
+      <c r="D12" s="58"/>
+      <c r="E12" s="58"/>
       <c r="F12" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="G12" s="66" t="s">
+      <c r="G12" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="H12" s="62"/>
-      <c r="I12" s="62"/>
-      <c r="J12" s="34" t="s">
+      <c r="H12" s="58"/>
+      <c r="I12" s="58"/>
+      <c r="J12" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="K12" s="66" t="s">
+      <c r="K12" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="L12" s="62"/>
-      <c r="M12" s="62"/>
-      <c r="N12" s="36" t="s">
+      <c r="L12" s="58"/>
+      <c r="M12" s="58"/>
+      <c r="N12" s="34" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="38"/>
-      <c r="C13" s="44"/>
-      <c r="D13" s="45"/>
-      <c r="E13" s="46"/>
+      <c r="B13" s="36"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="44"/>
       <c r="F13" s="26"/>
-      <c r="G13" s="47"/>
-      <c r="H13" s="47"/>
-      <c r="I13" s="48"/>
-      <c r="J13" s="35"/>
-      <c r="K13" s="67"/>
-      <c r="L13" s="67"/>
-      <c r="M13" s="67"/>
-      <c r="N13" s="35"/>
+      <c r="G13" s="45"/>
+      <c r="H13" s="45"/>
+      <c r="I13" s="46"/>
+      <c r="J13" s="33"/>
+      <c r="K13" s="63"/>
+      <c r="L13" s="63"/>
+      <c r="M13" s="63"/>
+      <c r="N13" s="33"/>
     </row>
     <row r="14" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="39"/>
-      <c r="C14" s="44"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="46"/>
+      <c r="B14" s="37"/>
+      <c r="C14" s="42"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="44"/>
       <c r="F14" s="26"/>
-      <c r="G14" s="44"/>
-      <c r="H14" s="45"/>
-      <c r="I14" s="45"/>
-      <c r="J14" s="35"/>
-      <c r="K14" s="55"/>
-      <c r="L14" s="55"/>
-      <c r="M14" s="55"/>
-      <c r="N14" s="37"/>
+      <c r="G14" s="42"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="43"/>
+      <c r="J14" s="33"/>
+      <c r="K14" s="53"/>
+      <c r="L14" s="53"/>
+      <c r="M14" s="53"/>
+      <c r="N14" s="35"/>
     </row>
     <row r="15" spans="1:15" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
-      <c r="B15" s="40"/>
-      <c r="C15" s="44"/>
-      <c r="D15" s="45"/>
-      <c r="E15" s="46"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="44"/>
       <c r="F15" s="26"/>
-      <c r="G15" s="47"/>
-      <c r="H15" s="47"/>
-      <c r="I15" s="48"/>
-      <c r="J15" s="35"/>
-      <c r="K15" s="49"/>
-      <c r="L15" s="49"/>
-      <c r="M15" s="49"/>
-      <c r="N15" s="37"/>
+      <c r="G15" s="45"/>
+      <c r="H15" s="45"/>
+      <c r="I15" s="46"/>
+      <c r="J15" s="33"/>
+      <c r="K15" s="47"/>
+      <c r="L15" s="47"/>
+      <c r="M15" s="47"/>
+      <c r="N15" s="35"/>
     </row>
     <row r="16" spans="1:15" s="7" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="3"/>
@@ -1554,266 +1543,266 @@
       <c r="N17"/>
     </row>
     <row r="18" spans="2:14" s="7" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="65" t="s">
+      <c r="B18" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="C18" s="65" t="s">
+      <c r="C18" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="D18" s="65"/>
-      <c r="E18" s="65"/>
-      <c r="F18" s="65"/>
-      <c r="G18" s="65"/>
+      <c r="D18" s="61"/>
+      <c r="E18" s="61"/>
+      <c r="F18" s="61"/>
+      <c r="G18" s="61"/>
       <c r="H18" s="25"/>
-      <c r="I18" s="65" t="s">
+      <c r="I18" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="J18" s="65" t="s">
+      <c r="J18" s="61" t="s">
         <v>11</v>
       </c>
       <c r="K18" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="L18" s="65" t="s">
+      <c r="L18" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="M18" s="63" t="s">
+      <c r="M18" s="59" t="s">
         <v>12</v>
       </c>
-      <c r="N18" s="63"/>
+      <c r="N18" s="59"/>
     </row>
     <row r="19" spans="2:14" s="7" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="56"/>
-      <c r="C19" s="56"/>
-      <c r="D19" s="56"/>
-      <c r="E19" s="56"/>
-      <c r="F19" s="56"/>
-      <c r="G19" s="56"/>
+      <c r="B19" s="54"/>
+      <c r="C19" s="54"/>
+      <c r="D19" s="54"/>
+      <c r="E19" s="54"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="54"/>
       <c r="H19" s="25"/>
-      <c r="I19" s="56"/>
-      <c r="J19" s="56"/>
+      <c r="I19" s="54"/>
+      <c r="J19" s="54"/>
       <c r="K19" s="31">
         <v>65</v>
       </c>
-      <c r="L19" s="56"/>
-      <c r="M19" s="64"/>
-      <c r="N19" s="64"/>
+      <c r="L19" s="54"/>
+      <c r="M19" s="60"/>
+      <c r="N19" s="60"/>
     </row>
     <row r="20" spans="2:14" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="28"/>
-      <c r="C20" s="60"/>
-      <c r="D20" s="60"/>
-      <c r="E20" s="60"/>
-      <c r="F20" s="60"/>
-      <c r="G20" s="60"/>
-      <c r="H20" s="60"/>
+      <c r="C20" s="93"/>
+      <c r="D20" s="93"/>
+      <c r="E20" s="93"/>
+      <c r="F20" s="93"/>
+      <c r="G20" s="93"/>
+      <c r="H20" s="93"/>
       <c r="I20" s="21"/>
       <c r="J20" s="21"/>
       <c r="K20" s="23"/>
       <c r="L20" s="23"/>
-      <c r="M20" s="59"/>
-      <c r="N20" s="59"/>
+      <c r="M20" s="94"/>
+      <c r="N20" s="94"/>
     </row>
     <row r="21" spans="2:14" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="28"/>
-      <c r="C21" s="60"/>
-      <c r="D21" s="60"/>
-      <c r="E21" s="60"/>
-      <c r="F21" s="60"/>
-      <c r="G21" s="60"/>
-      <c r="H21" s="60"/>
+      <c r="C21" s="93"/>
+      <c r="D21" s="93"/>
+      <c r="E21" s="93"/>
+      <c r="F21" s="93"/>
+      <c r="G21" s="93"/>
+      <c r="H21" s="93"/>
       <c r="I21" s="21"/>
       <c r="J21" s="21"/>
       <c r="K21" s="23"/>
       <c r="L21" s="23"/>
-      <c r="M21" s="59"/>
-      <c r="N21" s="59"/>
+      <c r="M21" s="94"/>
+      <c r="N21" s="94"/>
     </row>
     <row r="22" spans="2:14" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="32"/>
-      <c r="C22" s="60"/>
-      <c r="D22" s="60"/>
-      <c r="E22" s="60"/>
-      <c r="F22" s="60"/>
-      <c r="G22" s="60"/>
-      <c r="H22" s="60"/>
+      <c r="B22" s="28"/>
+      <c r="C22" s="93"/>
+      <c r="D22" s="93"/>
+      <c r="E22" s="93"/>
+      <c r="F22" s="93"/>
+      <c r="G22" s="93"/>
+      <c r="H22" s="93"/>
       <c r="I22" s="21"/>
       <c r="J22" s="21"/>
       <c r="K22" s="23"/>
       <c r="L22" s="23"/>
-      <c r="M22" s="59"/>
-      <c r="N22" s="59"/>
+      <c r="M22" s="94"/>
+      <c r="N22" s="94"/>
     </row>
     <row r="23" spans="2:14" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="33"/>
-      <c r="C23" s="60"/>
-      <c r="D23" s="60"/>
-      <c r="E23" s="60"/>
-      <c r="F23" s="60"/>
-      <c r="G23" s="60"/>
-      <c r="H23" s="60"/>
+      <c r="B23" s="28"/>
+      <c r="C23" s="93"/>
+      <c r="D23" s="93"/>
+      <c r="E23" s="93"/>
+      <c r="F23" s="93"/>
+      <c r="G23" s="93"/>
+      <c r="H23" s="93"/>
       <c r="I23" s="21"/>
       <c r="J23" s="21"/>
       <c r="K23" s="23"/>
       <c r="L23" s="23"/>
-      <c r="M23" s="59"/>
-      <c r="N23" s="59"/>
+      <c r="M23" s="94"/>
+      <c r="N23" s="94"/>
     </row>
     <row r="24" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="25" spans="2:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="26" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="56" t="s">
+      <c r="B26" s="54" t="s">
         <v>16</v>
       </c>
-      <c r="C26" s="56"/>
-      <c r="D26" s="56"/>
-      <c r="E26" s="56"/>
-      <c r="F26" s="56"/>
-      <c r="G26" s="56"/>
+      <c r="C26" s="54"/>
+      <c r="D26" s="54"/>
+      <c r="E26" s="54"/>
+      <c r="F26" s="54"/>
+      <c r="G26" s="54"/>
       <c r="H26" s="20"/>
-      <c r="K26" s="65" t="s">
+      <c r="K26" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="L26" s="65"/>
+      <c r="L26" s="61"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B27" s="81" t="s">
+      <c r="B27" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="C27" s="81"/>
+      <c r="C27" s="77"/>
       <c r="D27" s="13"/>
-      <c r="E27" s="83" t="s">
+      <c r="E27" s="79" t="s">
         <v>23</v>
       </c>
-      <c r="F27" s="83"/>
-      <c r="G27" s="83"/>
+      <c r="F27" s="79"/>
+      <c r="G27" s="79"/>
       <c r="H27" s="17"/>
-      <c r="K27" s="75" t="s">
+      <c r="K27" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="L27" s="78">
-        <f>SUM(L20:L23)</f>
+      <c r="L27" s="74">
+        <f>SUM(L20:L20)</f>
         <v>0</v>
       </c>
       <c r="N27" s="24"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B28" s="82"/>
-      <c r="C28" s="82"/>
+      <c r="B28" s="78"/>
+      <c r="C28" s="78"/>
       <c r="D28" s="14"/>
-      <c r="E28" s="84"/>
-      <c r="F28" s="84"/>
-      <c r="G28" s="84"/>
+      <c r="E28" s="80"/>
+      <c r="F28" s="80"/>
+      <c r="G28" s="80"/>
       <c r="H28" s="17"/>
-      <c r="K28" s="76"/>
-      <c r="L28" s="79"/>
+      <c r="K28" s="72"/>
+      <c r="L28" s="75"/>
     </row>
     <row r="29" spans="2:14" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="85" t="s">
+      <c r="B29" s="81" t="s">
         <v>17</v>
       </c>
-      <c r="C29" s="86"/>
+      <c r="C29" s="82"/>
       <c r="D29" s="13"/>
-      <c r="E29" s="87" t="s">
+      <c r="E29" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="F29" s="83"/>
-      <c r="G29" s="83"/>
+      <c r="F29" s="79"/>
+      <c r="G29" s="79"/>
       <c r="H29" s="18"/>
-      <c r="K29" s="77"/>
-      <c r="L29" s="80"/>
+      <c r="K29" s="73"/>
+      <c r="L29" s="76"/>
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B30" s="85"/>
-      <c r="C30" s="86"/>
+      <c r="B30" s="81"/>
+      <c r="C30" s="82"/>
       <c r="D30" s="14"/>
-      <c r="E30" s="84"/>
-      <c r="F30" s="84"/>
-      <c r="G30" s="84"/>
+      <c r="E30" s="80"/>
+      <c r="F30" s="80"/>
+      <c r="G30" s="80"/>
       <c r="H30" s="18"/>
-      <c r="K30" s="75" t="s">
+      <c r="K30" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="L30" s="88"/>
+      <c r="L30" s="84"/>
     </row>
     <row r="31" spans="2:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="81" t="s">
+      <c r="B31" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="C31" s="81"/>
+      <c r="C31" s="77"/>
       <c r="D31" s="13"/>
-      <c r="E31" s="95" t="s">
+      <c r="E31" s="91" t="s">
         <v>23</v>
       </c>
-      <c r="F31" s="95"/>
-      <c r="G31" s="95"/>
+      <c r="F31" s="91"/>
+      <c r="G31" s="91"/>
       <c r="H31" s="8"/>
-      <c r="K31" s="76"/>
-      <c r="L31" s="89"/>
+      <c r="K31" s="72"/>
+      <c r="L31" s="85"/>
     </row>
     <row r="32" spans="2:14" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="82"/>
-      <c r="C32" s="82"/>
+      <c r="B32" s="78"/>
+      <c r="C32" s="78"/>
       <c r="D32" s="14"/>
-      <c r="E32" s="96"/>
-      <c r="F32" s="96"/>
-      <c r="G32" s="96"/>
+      <c r="E32" s="92"/>
+      <c r="F32" s="92"/>
+      <c r="G32" s="92"/>
       <c r="H32" s="8"/>
-      <c r="K32" s="77"/>
-      <c r="L32" s="90"/>
+      <c r="K32" s="73"/>
+      <c r="L32" s="86"/>
     </row>
     <row r="33" spans="2:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="91" t="s">
+      <c r="B33" s="87" t="s">
         <v>27</v>
       </c>
-      <c r="C33" s="91"/>
+      <c r="C33" s="87"/>
       <c r="D33" s="16"/>
-      <c r="E33" s="93" t="s">
+      <c r="E33" s="89" t="s">
         <v>22</v>
       </c>
-      <c r="F33" s="93"/>
-      <c r="G33" s="93"/>
+      <c r="F33" s="89"/>
+      <c r="G33" s="89"/>
       <c r="H33" s="8"/>
-      <c r="K33" s="75" t="s">
+      <c r="K33" s="71" t="s">
         <v>20</v>
       </c>
-      <c r="L33" s="88">
+      <c r="L33" s="84">
         <f>L27</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:14" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="92"/>
-      <c r="C34" s="92"/>
+      <c r="B34" s="88"/>
+      <c r="C34" s="88"/>
       <c r="D34" s="15"/>
-      <c r="E34" s="94"/>
-      <c r="F34" s="94"/>
-      <c r="G34" s="94"/>
+      <c r="E34" s="90"/>
+      <c r="F34" s="90"/>
+      <c r="G34" s="90"/>
       <c r="H34" s="8"/>
-      <c r="K34" s="76"/>
-      <c r="L34" s="89"/>
+      <c r="K34" s="72"/>
+      <c r="L34" s="85"/>
     </row>
     <row r="35" spans="2:14" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="69" t="s">
+      <c r="B35" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="C35" s="70"/>
-      <c r="D35" s="70"/>
-      <c r="E35" s="70"/>
-      <c r="F35" s="70"/>
-      <c r="G35" s="71"/>
+      <c r="C35" s="66"/>
+      <c r="D35" s="66"/>
+      <c r="E35" s="66"/>
+      <c r="F35" s="66"/>
+      <c r="G35" s="67"/>
       <c r="H35" s="19"/>
       <c r="J35" s="11"/>
-      <c r="K35" s="77"/>
-      <c r="L35" s="90"/>
+      <c r="K35" s="73"/>
+      <c r="L35" s="86"/>
     </row>
     <row r="36" spans="2:14" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="72"/>
-      <c r="C36" s="73"/>
-      <c r="D36" s="73"/>
-      <c r="E36" s="73"/>
-      <c r="F36" s="73"/>
-      <c r="G36" s="74"/>
+      <c r="B36" s="68"/>
+      <c r="C36" s="69"/>
+      <c r="D36" s="69"/>
+      <c r="E36" s="69"/>
+      <c r="F36" s="69"/>
+      <c r="G36" s="70"/>
       <c r="H36" s="19"/>
       <c r="K36" s="12"/>
       <c r="L36" s="12"/>
@@ -1871,26 +1860,26 @@
     <row r="46" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="47" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="49" spans="9:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="I49" s="68" t="s">
+      <c r="I49" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="J49" s="68"/>
-      <c r="K49" s="68"/>
-      <c r="L49" s="68"/>
+      <c r="J49" s="64"/>
+      <c r="K49" s="64"/>
+      <c r="L49" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="54">
     <mergeCell ref="K26:L26"/>
     <mergeCell ref="B26:G26"/>
     <mergeCell ref="B18:B19"/>
-    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="C20:H20"/>
+    <mergeCell ref="M20:N20"/>
     <mergeCell ref="C23:H23"/>
     <mergeCell ref="M23:N23"/>
-    <mergeCell ref="C20:H20"/>
-    <mergeCell ref="M20:N20"/>
     <mergeCell ref="C21:H21"/>
     <mergeCell ref="M21:N21"/>
     <mergeCell ref="C22:H22"/>
+    <mergeCell ref="M22:N22"/>
     <mergeCell ref="I49:L49"/>
     <mergeCell ref="B35:G36"/>
     <mergeCell ref="K27:K29"/>

--- a/utils/po_templates/po_template.xlsx
+++ b/utils/po_templates/po_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbolanos\Desktop\projects\cps-tool\utils\po_templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2DA0B71-ED23-42A0-8A63-CE9ACF51D50A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB92A7EE-E25B-41E8-83D5-3977CC67B3BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -117,9 +117,6 @@
     <t>Unit Price/ hr</t>
   </si>
   <si>
-    <t>Signature Jean Doe</t>
-  </si>
-  <si>
     <t>TBP</t>
   </si>
   <si>
@@ -128,6 +125,9 @@
   <si>
     <t>*** The export box supplied by Toyota should never be opened unless specific instructions from CPS Africa are given to do so.
 Your entity will be held responsible if you fail to comply ***</t>
+  </si>
+  <si>
+    <t>Signature C. Johnson</t>
   </si>
 </sst>
 </file>
@@ -719,6 +719,132 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -735,12 +861,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -764,128 +884,8 @@
     <xf numFmtId="0" fontId="9" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1296,12 +1296,12 @@
       <c r="H1" s="6"/>
       <c r="I1" s="6"/>
       <c r="J1" s="6"/>
-      <c r="K1" s="39" t="s">
+      <c r="K1" s="81" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="39"/>
-      <c r="M1" s="39"/>
-      <c r="N1" s="39"/>
+      <c r="L1" s="81"/>
+      <c r="M1" s="81"/>
+      <c r="N1" s="81"/>
     </row>
     <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E2" s="6"/>
@@ -1310,10 +1310,10 @@
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
       <c r="J2" s="6"/>
-      <c r="K2" s="39"/>
-      <c r="L2" s="39"/>
-      <c r="M2" s="39"/>
-      <c r="N2" s="39"/>
+      <c r="K2" s="81"/>
+      <c r="L2" s="81"/>
+      <c r="M2" s="81"/>
+      <c r="N2" s="81"/>
     </row>
     <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E3" s="6"/>
@@ -1329,88 +1329,88 @@
       <c r="O3" s="6"/>
     </row>
     <row r="4" spans="1:15" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="K4" s="50" t="s">
+      <c r="K4" s="90" t="s">
         <v>0</v>
       </c>
-      <c r="L4" s="40"/>
-      <c r="M4" s="40"/>
-      <c r="N4" s="40"/>
+      <c r="L4" s="82"/>
+      <c r="M4" s="82"/>
+      <c r="N4" s="82"/>
     </row>
     <row r="5" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="54" t="s">
+      <c r="B5" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="54"/>
+      <c r="C5" s="40"/>
       <c r="D5" s="20"/>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
       <c r="I5" s="10"/>
-      <c r="K5" s="49"/>
-      <c r="L5" s="41"/>
-      <c r="M5" s="41"/>
-      <c r="N5" s="41"/>
+      <c r="K5" s="89"/>
+      <c r="L5" s="83"/>
+      <c r="M5" s="83"/>
+      <c r="N5" s="83"/>
     </row>
     <row r="6" spans="1:15" s="1" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="51"/>
-      <c r="C6" s="51"/>
+      <c r="B6" s="91"/>
+      <c r="C6" s="91"/>
       <c r="D6" s="29"/>
       <c r="E6" s="30"/>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
       <c r="H6" s="7"/>
       <c r="I6" s="4"/>
-      <c r="K6" s="48" t="s">
+      <c r="K6" s="88" t="s">
         <v>15</v>
       </c>
-      <c r="L6" s="55"/>
-      <c r="M6" s="55"/>
-      <c r="N6" s="55"/>
+      <c r="L6" s="94"/>
+      <c r="M6" s="94"/>
+      <c r="N6" s="94"/>
     </row>
     <row r="7" spans="1:15" s="1" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="52"/>
-      <c r="C7" s="52"/>
+      <c r="B7" s="92"/>
+      <c r="C7" s="92"/>
       <c r="D7" s="29"/>
       <c r="E7" s="30"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
       <c r="I7" s="4"/>
-      <c r="K7" s="49"/>
-      <c r="L7" s="41"/>
-      <c r="M7" s="41"/>
-      <c r="N7" s="41"/>
+      <c r="K7" s="89"/>
+      <c r="L7" s="83"/>
+      <c r="M7" s="83"/>
+      <c r="N7" s="83"/>
     </row>
     <row r="8" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="52"/>
-      <c r="C8" s="52"/>
+      <c r="B8" s="92"/>
+      <c r="C8" s="92"/>
       <c r="D8" s="29"/>
       <c r="E8" s="30"/>
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
       <c r="I8" s="4"/>
-      <c r="K8" s="56" t="s">
+      <c r="K8" s="72" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="55"/>
-      <c r="M8" s="55"/>
-      <c r="N8" s="55"/>
+      <c r="L8" s="94"/>
+      <c r="M8" s="94"/>
+      <c r="N8" s="94"/>
     </row>
     <row r="9" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="52"/>
-      <c r="C9" s="52"/>
+      <c r="B9" s="92"/>
+      <c r="C9" s="92"/>
       <c r="D9" s="29"/>
       <c r="E9" s="30"/>
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
       <c r="I9" s="4"/>
-      <c r="K9" s="56"/>
-      <c r="L9" s="41"/>
-      <c r="M9" s="41"/>
-      <c r="N9" s="41"/>
+      <c r="K9" s="72"/>
+      <c r="L9" s="83"/>
+      <c r="M9" s="83"/>
+      <c r="N9" s="83"/>
     </row>
     <row r="10" spans="1:15" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="7"/>
@@ -1441,75 +1441,75 @@
       <c r="B12" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="57" t="s">
+      <c r="C12" s="73" t="s">
         <v>2</v>
       </c>
-      <c r="D12" s="58"/>
-      <c r="E12" s="58"/>
+      <c r="D12" s="74"/>
+      <c r="E12" s="74"/>
       <c r="F12" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="G12" s="62" t="s">
+      <c r="G12" s="77" t="s">
         <v>2</v>
       </c>
-      <c r="H12" s="58"/>
-      <c r="I12" s="58"/>
+      <c r="H12" s="74"/>
+      <c r="I12" s="74"/>
       <c r="J12" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="K12" s="62" t="s">
+      <c r="K12" s="77" t="s">
         <v>2</v>
       </c>
-      <c r="L12" s="58"/>
-      <c r="M12" s="58"/>
+      <c r="L12" s="74"/>
+      <c r="M12" s="74"/>
       <c r="N12" s="34" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="36"/>
-      <c r="C13" s="42"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="44"/>
+      <c r="C13" s="84"/>
+      <c r="D13" s="85"/>
+      <c r="E13" s="86"/>
       <c r="F13" s="26"/>
-      <c r="G13" s="45"/>
-      <c r="H13" s="45"/>
-      <c r="I13" s="46"/>
+      <c r="G13" s="79"/>
+      <c r="H13" s="79"/>
+      <c r="I13" s="80"/>
       <c r="J13" s="33"/>
-      <c r="K13" s="63"/>
-      <c r="L13" s="63"/>
-      <c r="M13" s="63"/>
+      <c r="K13" s="78"/>
+      <c r="L13" s="78"/>
+      <c r="M13" s="78"/>
       <c r="N13" s="33"/>
     </row>
     <row r="14" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="37"/>
-      <c r="C14" s="42"/>
-      <c r="D14" s="43"/>
-      <c r="E14" s="44"/>
+      <c r="C14" s="84"/>
+      <c r="D14" s="85"/>
+      <c r="E14" s="86"/>
       <c r="F14" s="26"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="43"/>
-      <c r="I14" s="43"/>
+      <c r="G14" s="84"/>
+      <c r="H14" s="85"/>
+      <c r="I14" s="85"/>
       <c r="J14" s="33"/>
-      <c r="K14" s="53"/>
-      <c r="L14" s="53"/>
-      <c r="M14" s="53"/>
+      <c r="K14" s="93"/>
+      <c r="L14" s="93"/>
+      <c r="M14" s="93"/>
       <c r="N14" s="35"/>
     </row>
     <row r="15" spans="1:15" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
       <c r="B15" s="38"/>
-      <c r="C15" s="42"/>
-      <c r="D15" s="43"/>
-      <c r="E15" s="44"/>
+      <c r="C15" s="84"/>
+      <c r="D15" s="85"/>
+      <c r="E15" s="86"/>
       <c r="F15" s="26"/>
-      <c r="G15" s="45"/>
-      <c r="H15" s="45"/>
-      <c r="I15" s="46"/>
+      <c r="G15" s="79"/>
+      <c r="H15" s="79"/>
+      <c r="I15" s="80"/>
       <c r="J15" s="33"/>
-      <c r="K15" s="47"/>
-      <c r="L15" s="47"/>
-      <c r="M15" s="47"/>
+      <c r="K15" s="87"/>
+      <c r="L15" s="87"/>
+      <c r="M15" s="87"/>
       <c r="N15" s="35"/>
     </row>
     <row r="16" spans="1:15" s="7" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
@@ -1543,266 +1543,266 @@
       <c r="N17"/>
     </row>
     <row r="18" spans="2:14" s="7" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="61" t="s">
+      <c r="B18" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="C18" s="61" t="s">
+      <c r="C18" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="D18" s="61"/>
-      <c r="E18" s="61"/>
-      <c r="F18" s="61"/>
-      <c r="G18" s="61"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="39"/>
       <c r="H18" s="25"/>
-      <c r="I18" s="61" t="s">
+      <c r="I18" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="J18" s="61" t="s">
+      <c r="J18" s="39" t="s">
         <v>11</v>
       </c>
       <c r="K18" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="L18" s="61" t="s">
+      <c r="L18" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="M18" s="59" t="s">
+      <c r="M18" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="N18" s="59"/>
+      <c r="N18" s="75"/>
     </row>
     <row r="19" spans="2:14" s="7" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="54"/>
-      <c r="C19" s="54"/>
-      <c r="D19" s="54"/>
-      <c r="E19" s="54"/>
-      <c r="F19" s="54"/>
-      <c r="G19" s="54"/>
+      <c r="B19" s="40"/>
+      <c r="C19" s="40"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="40"/>
+      <c r="F19" s="40"/>
+      <c r="G19" s="40"/>
       <c r="H19" s="25"/>
-      <c r="I19" s="54"/>
-      <c r="J19" s="54"/>
+      <c r="I19" s="40"/>
+      <c r="J19" s="40"/>
       <c r="K19" s="31">
         <v>65</v>
       </c>
-      <c r="L19" s="54"/>
-      <c r="M19" s="60"/>
-      <c r="N19" s="60"/>
+      <c r="L19" s="40"/>
+      <c r="M19" s="76"/>
+      <c r="N19" s="76"/>
     </row>
     <row r="20" spans="2:14" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="28"/>
-      <c r="C20" s="93"/>
-      <c r="D20" s="93"/>
-      <c r="E20" s="93"/>
-      <c r="F20" s="93"/>
-      <c r="G20" s="93"/>
-      <c r="H20" s="93"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="41"/>
       <c r="I20" s="21"/>
       <c r="J20" s="21"/>
       <c r="K20" s="23"/>
       <c r="L20" s="23"/>
-      <c r="M20" s="94"/>
-      <c r="N20" s="94"/>
+      <c r="M20" s="42"/>
+      <c r="N20" s="42"/>
     </row>
     <row r="21" spans="2:14" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="28"/>
-      <c r="C21" s="93"/>
-      <c r="D21" s="93"/>
-      <c r="E21" s="93"/>
-      <c r="F21" s="93"/>
-      <c r="G21" s="93"/>
-      <c r="H21" s="93"/>
+      <c r="C21" s="41"/>
+      <c r="D21" s="41"/>
+      <c r="E21" s="41"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="41"/>
+      <c r="H21" s="41"/>
       <c r="I21" s="21"/>
       <c r="J21" s="21"/>
       <c r="K21" s="23"/>
       <c r="L21" s="23"/>
-      <c r="M21" s="94"/>
-      <c r="N21" s="94"/>
+      <c r="M21" s="42"/>
+      <c r="N21" s="42"/>
     </row>
     <row r="22" spans="2:14" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="28"/>
-      <c r="C22" s="93"/>
-      <c r="D22" s="93"/>
-      <c r="E22" s="93"/>
-      <c r="F22" s="93"/>
-      <c r="G22" s="93"/>
-      <c r="H22" s="93"/>
+      <c r="C22" s="41"/>
+      <c r="D22" s="41"/>
+      <c r="E22" s="41"/>
+      <c r="F22" s="41"/>
+      <c r="G22" s="41"/>
+      <c r="H22" s="41"/>
       <c r="I22" s="21"/>
       <c r="J22" s="21"/>
       <c r="K22" s="23"/>
       <c r="L22" s="23"/>
-      <c r="M22" s="94"/>
-      <c r="N22" s="94"/>
+      <c r="M22" s="42"/>
+      <c r="N22" s="42"/>
     </row>
     <row r="23" spans="2:14" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="28"/>
-      <c r="C23" s="93"/>
-      <c r="D23" s="93"/>
-      <c r="E23" s="93"/>
-      <c r="F23" s="93"/>
-      <c r="G23" s="93"/>
-      <c r="H23" s="93"/>
+      <c r="C23" s="41"/>
+      <c r="D23" s="41"/>
+      <c r="E23" s="41"/>
+      <c r="F23" s="41"/>
+      <c r="G23" s="41"/>
+      <c r="H23" s="41"/>
       <c r="I23" s="21"/>
       <c r="J23" s="21"/>
       <c r="K23" s="23"/>
       <c r="L23" s="23"/>
-      <c r="M23" s="94"/>
-      <c r="N23" s="94"/>
+      <c r="M23" s="42"/>
+      <c r="N23" s="42"/>
     </row>
     <row r="24" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="25" spans="2:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="26" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="54" t="s">
+      <c r="B26" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="C26" s="54"/>
-      <c r="D26" s="54"/>
-      <c r="E26" s="54"/>
-      <c r="F26" s="54"/>
-      <c r="G26" s="54"/>
+      <c r="C26" s="40"/>
+      <c r="D26" s="40"/>
+      <c r="E26" s="40"/>
+      <c r="F26" s="40"/>
+      <c r="G26" s="40"/>
       <c r="H26" s="20"/>
-      <c r="K26" s="61" t="s">
+      <c r="K26" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="L26" s="61"/>
+      <c r="L26" s="39"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B27" s="77" t="s">
+      <c r="B27" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="C27" s="77"/>
+      <c r="C27" s="56"/>
       <c r="D27" s="13"/>
-      <c r="E27" s="79" t="s">
+      <c r="E27" s="58" t="s">
         <v>23</v>
       </c>
-      <c r="F27" s="79"/>
-      <c r="G27" s="79"/>
+      <c r="F27" s="58"/>
+      <c r="G27" s="58"/>
       <c r="H27" s="17"/>
-      <c r="K27" s="71" t="s">
+      <c r="K27" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="L27" s="74">
+      <c r="L27" s="53">
         <f>SUM(L20:L20)</f>
         <v>0</v>
       </c>
       <c r="N27" s="24"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B28" s="78"/>
-      <c r="C28" s="78"/>
+      <c r="B28" s="57"/>
+      <c r="C28" s="57"/>
       <c r="D28" s="14"/>
-      <c r="E28" s="80"/>
-      <c r="F28" s="80"/>
-      <c r="G28" s="80"/>
+      <c r="E28" s="59"/>
+      <c r="F28" s="59"/>
+      <c r="G28" s="59"/>
       <c r="H28" s="17"/>
-      <c r="K28" s="72"/>
-      <c r="L28" s="75"/>
+      <c r="K28" s="51"/>
+      <c r="L28" s="54"/>
     </row>
     <row r="29" spans="2:14" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="81" t="s">
+      <c r="B29" s="60" t="s">
         <v>17</v>
       </c>
-      <c r="C29" s="82"/>
+      <c r="C29" s="61"/>
       <c r="D29" s="13"/>
-      <c r="E29" s="83" t="s">
+      <c r="E29" s="62" t="s">
+        <v>25</v>
+      </c>
+      <c r="F29" s="58"/>
+      <c r="G29" s="58"/>
+      <c r="H29" s="18"/>
+      <c r="K29" s="52"/>
+      <c r="L29" s="55"/>
+    </row>
+    <row r="30" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B30" s="60"/>
+      <c r="C30" s="61"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="59"/>
+      <c r="F30" s="59"/>
+      <c r="G30" s="59"/>
+      <c r="H30" s="18"/>
+      <c r="K30" s="50" t="s">
+        <v>8</v>
+      </c>
+      <c r="L30" s="63"/>
+    </row>
+    <row r="31" spans="2:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B31" s="56" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="56"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="70" t="s">
+        <v>23</v>
+      </c>
+      <c r="F31" s="70"/>
+      <c r="G31" s="70"/>
+      <c r="H31" s="8"/>
+      <c r="K31" s="51"/>
+      <c r="L31" s="64"/>
+    </row>
+    <row r="32" spans="2:14" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="57"/>
+      <c r="C32" s="57"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="71"/>
+      <c r="F32" s="71"/>
+      <c r="G32" s="71"/>
+      <c r="H32" s="8"/>
+      <c r="K32" s="52"/>
+      <c r="L32" s="65"/>
+    </row>
+    <row r="33" spans="2:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B33" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="F29" s="79"/>
-      <c r="G29" s="79"/>
-      <c r="H29" s="18"/>
-      <c r="K29" s="73"/>
-      <c r="L29" s="76"/>
-    </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B30" s="81"/>
-      <c r="C30" s="82"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="80"/>
-      <c r="F30" s="80"/>
-      <c r="G30" s="80"/>
-      <c r="H30" s="18"/>
-      <c r="K30" s="71" t="s">
-        <v>8</v>
-      </c>
-      <c r="L30" s="84"/>
-    </row>
-    <row r="31" spans="2:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="77" t="s">
-        <v>18</v>
-      </c>
-      <c r="C31" s="77"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="91" t="s">
-        <v>23</v>
-      </c>
-      <c r="F31" s="91"/>
-      <c r="G31" s="91"/>
-      <c r="H31" s="8"/>
-      <c r="K31" s="72"/>
-      <c r="L31" s="85"/>
-    </row>
-    <row r="32" spans="2:14" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="78"/>
-      <c r="C32" s="78"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="92"/>
-      <c r="F32" s="92"/>
-      <c r="G32" s="92"/>
-      <c r="H32" s="8"/>
-      <c r="K32" s="73"/>
-      <c r="L32" s="86"/>
-    </row>
-    <row r="33" spans="2:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="C33" s="87"/>
+      <c r="C33" s="66"/>
       <c r="D33" s="16"/>
-      <c r="E33" s="89" t="s">
+      <c r="E33" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="F33" s="89"/>
-      <c r="G33" s="89"/>
+      <c r="F33" s="68"/>
+      <c r="G33" s="68"/>
       <c r="H33" s="8"/>
-      <c r="K33" s="71" t="s">
+      <c r="K33" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="L33" s="84">
+      <c r="L33" s="63">
         <f>L27</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:14" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="88"/>
-      <c r="C34" s="88"/>
+      <c r="B34" s="67"/>
+      <c r="C34" s="67"/>
       <c r="D34" s="15"/>
-      <c r="E34" s="90"/>
-      <c r="F34" s="90"/>
-      <c r="G34" s="90"/>
+      <c r="E34" s="69"/>
+      <c r="F34" s="69"/>
+      <c r="G34" s="69"/>
       <c r="H34" s="8"/>
-      <c r="K34" s="72"/>
-      <c r="L34" s="85"/>
+      <c r="K34" s="51"/>
+      <c r="L34" s="64"/>
     </row>
     <row r="35" spans="2:14" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="65" t="s">
-        <v>28</v>
-      </c>
-      <c r="C35" s="66"/>
-      <c r="D35" s="66"/>
-      <c r="E35" s="66"/>
-      <c r="F35" s="66"/>
-      <c r="G35" s="67"/>
+      <c r="B35" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="C35" s="45"/>
+      <c r="D35" s="45"/>
+      <c r="E35" s="45"/>
+      <c r="F35" s="45"/>
+      <c r="G35" s="46"/>
       <c r="H35" s="19"/>
       <c r="J35" s="11"/>
-      <c r="K35" s="73"/>
-      <c r="L35" s="86"/>
+      <c r="K35" s="52"/>
+      <c r="L35" s="65"/>
     </row>
     <row r="36" spans="2:14" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="68"/>
-      <c r="C36" s="69"/>
-      <c r="D36" s="69"/>
-      <c r="E36" s="69"/>
-      <c r="F36" s="69"/>
-      <c r="G36" s="70"/>
+      <c r="B36" s="47"/>
+      <c r="C36" s="48"/>
+      <c r="D36" s="48"/>
+      <c r="E36" s="48"/>
+      <c r="F36" s="48"/>
+      <c r="G36" s="49"/>
       <c r="H36" s="19"/>
       <c r="K36" s="12"/>
       <c r="L36" s="12"/>
@@ -1860,26 +1860,42 @@
     <row r="46" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="47" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="49" spans="9:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="I49" s="64" t="s">
-        <v>25</v>
-      </c>
-      <c r="J49" s="64"/>
-      <c r="K49" s="64"/>
-      <c r="L49" s="64"/>
+      <c r="I49" s="43" t="s">
+        <v>28</v>
+      </c>
+      <c r="J49" s="43"/>
+      <c r="K49" s="43"/>
+      <c r="L49" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="54">
-    <mergeCell ref="K26:L26"/>
-    <mergeCell ref="B26:G26"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C20:H20"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="C23:H23"/>
-    <mergeCell ref="M23:N23"/>
-    <mergeCell ref="C21:H21"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="C22:H22"/>
-    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="K1:N2"/>
+    <mergeCell ref="L4:N5"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="K15:M15"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C9"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="K14:M14"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="L6:N7"/>
+    <mergeCell ref="L8:N9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="M18:N19"/>
+    <mergeCell ref="L18:L19"/>
+    <mergeCell ref="C18:G19"/>
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="J18:J19"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="K13:M13"/>
+    <mergeCell ref="G13:I13"/>
     <mergeCell ref="I49:L49"/>
     <mergeCell ref="B35:G36"/>
     <mergeCell ref="K27:K29"/>
@@ -1896,33 +1912,17 @@
     <mergeCell ref="E33:G34"/>
     <mergeCell ref="B31:C32"/>
     <mergeCell ref="E31:G32"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="M18:N19"/>
-    <mergeCell ref="L18:L19"/>
-    <mergeCell ref="C18:G19"/>
-    <mergeCell ref="I18:I19"/>
-    <mergeCell ref="J18:J19"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="K13:M13"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="K1:N2"/>
-    <mergeCell ref="L4:N5"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="K15:M15"/>
-    <mergeCell ref="K6:K7"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C9"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="L6:N7"/>
-    <mergeCell ref="L8:N9"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="B26:G26"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C20:H20"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="C23:H23"/>
+    <mergeCell ref="M23:N23"/>
+    <mergeCell ref="C21:H21"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="C22:H22"/>
+    <mergeCell ref="M22:N22"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="F13:F15">
@@ -1950,12 +1950,13 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a52bf194-6401-462b-9261-416d3ab8d515">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2188,19 +2189,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a52bf194-6401-462b-9261-416d3ab8d515">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B73DC9C3-8993-467B-9C7F-6F901699B4B8}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B752BE4-1396-4BCB-B02F-A8A256B5B09D}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="a52bf194-6401-462b-9261-416d3ab8d515"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2225,11 +2227,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B752BE4-1396-4BCB-B02F-A8A256B5B09D}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B73DC9C3-8993-467B-9C7F-6F901699B4B8}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="a52bf194-6401-462b-9261-416d3ab8d515"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/utils/po_templates/po_template.xlsx
+++ b/utils/po_templates/po_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbolanos\Desktop\projects\cps-tool\utils\po_templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB92A7EE-E25B-41E8-83D5-3977CC67B3BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{035B9021-658B-4CBC-89F6-481794FB1178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="28">
   <si>
     <t>Date</t>
   </si>
@@ -115,9 +115,6 @@
   </si>
   <si>
     <t>Unit Price/ hr</t>
-  </si>
-  <si>
-    <t>TBP</t>
   </si>
   <si>
     <t>Stickers</t>
@@ -719,173 +716,173 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1296,12 +1293,12 @@
       <c r="H1" s="6"/>
       <c r="I1" s="6"/>
       <c r="J1" s="6"/>
-      <c r="K1" s="81" t="s">
+      <c r="K1" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="81"/>
-      <c r="M1" s="81"/>
-      <c r="N1" s="81"/>
+      <c r="L1" s="39"/>
+      <c r="M1" s="39"/>
+      <c r="N1" s="39"/>
     </row>
     <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E2" s="6"/>
@@ -1310,10 +1307,10 @@
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
       <c r="J2" s="6"/>
-      <c r="K2" s="81"/>
-      <c r="L2" s="81"/>
-      <c r="M2" s="81"/>
-      <c r="N2" s="81"/>
+      <c r="K2" s="39"/>
+      <c r="L2" s="39"/>
+      <c r="M2" s="39"/>
+      <c r="N2" s="39"/>
     </row>
     <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E3" s="6"/>
@@ -1329,88 +1326,88 @@
       <c r="O3" s="6"/>
     </row>
     <row r="4" spans="1:15" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="K4" s="90" t="s">
+      <c r="K4" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="L4" s="82"/>
-      <c r="M4" s="82"/>
-      <c r="N4" s="82"/>
+      <c r="L4" s="40"/>
+      <c r="M4" s="40"/>
+      <c r="N4" s="40"/>
     </row>
     <row r="5" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="40" t="s">
+      <c r="B5" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="40"/>
+      <c r="C5" s="54"/>
       <c r="D5" s="20"/>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
       <c r="I5" s="10"/>
-      <c r="K5" s="89"/>
-      <c r="L5" s="83"/>
-      <c r="M5" s="83"/>
-      <c r="N5" s="83"/>
+      <c r="K5" s="49"/>
+      <c r="L5" s="41"/>
+      <c r="M5" s="41"/>
+      <c r="N5" s="41"/>
     </row>
     <row r="6" spans="1:15" s="1" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="91"/>
-      <c r="C6" s="91"/>
+      <c r="B6" s="51"/>
+      <c r="C6" s="51"/>
       <c r="D6" s="29"/>
       <c r="E6" s="30"/>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
       <c r="H6" s="7"/>
       <c r="I6" s="4"/>
-      <c r="K6" s="88" t="s">
+      <c r="K6" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="L6" s="94"/>
-      <c r="M6" s="94"/>
-      <c r="N6" s="94"/>
+      <c r="L6" s="55"/>
+      <c r="M6" s="55"/>
+      <c r="N6" s="55"/>
     </row>
     <row r="7" spans="1:15" s="1" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="92"/>
-      <c r="C7" s="92"/>
+      <c r="B7" s="52"/>
+      <c r="C7" s="52"/>
       <c r="D7" s="29"/>
       <c r="E7" s="30"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
       <c r="I7" s="4"/>
-      <c r="K7" s="89"/>
-      <c r="L7" s="83"/>
-      <c r="M7" s="83"/>
-      <c r="N7" s="83"/>
+      <c r="K7" s="49"/>
+      <c r="L7" s="41"/>
+      <c r="M7" s="41"/>
+      <c r="N7" s="41"/>
     </row>
     <row r="8" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="92"/>
-      <c r="C8" s="92"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="52"/>
       <c r="D8" s="29"/>
       <c r="E8" s="30"/>
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
       <c r="I8" s="4"/>
-      <c r="K8" s="72" t="s">
+      <c r="K8" s="56" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="94"/>
-      <c r="M8" s="94"/>
-      <c r="N8" s="94"/>
+      <c r="L8" s="55"/>
+      <c r="M8" s="55"/>
+      <c r="N8" s="55"/>
     </row>
     <row r="9" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="92"/>
-      <c r="C9" s="92"/>
+      <c r="B9" s="52"/>
+      <c r="C9" s="52"/>
       <c r="D9" s="29"/>
       <c r="E9" s="30"/>
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
       <c r="I9" s="4"/>
-      <c r="K9" s="72"/>
-      <c r="L9" s="83"/>
-      <c r="M9" s="83"/>
-      <c r="N9" s="83"/>
+      <c r="K9" s="56"/>
+      <c r="L9" s="41"/>
+      <c r="M9" s="41"/>
+      <c r="N9" s="41"/>
     </row>
     <row r="10" spans="1:15" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="7"/>
@@ -1441,75 +1438,75 @@
       <c r="B12" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="73" t="s">
+      <c r="C12" s="57" t="s">
         <v>2</v>
       </c>
-      <c r="D12" s="74"/>
-      <c r="E12" s="74"/>
+      <c r="D12" s="58"/>
+      <c r="E12" s="58"/>
       <c r="F12" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="G12" s="77" t="s">
+      <c r="G12" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="H12" s="74"/>
-      <c r="I12" s="74"/>
+      <c r="H12" s="58"/>
+      <c r="I12" s="58"/>
       <c r="J12" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="K12" s="77" t="s">
+      <c r="K12" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="L12" s="74"/>
-      <c r="M12" s="74"/>
+      <c r="L12" s="58"/>
+      <c r="M12" s="58"/>
       <c r="N12" s="34" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="36"/>
-      <c r="C13" s="84"/>
-      <c r="D13" s="85"/>
-      <c r="E13" s="86"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="44"/>
       <c r="F13" s="26"/>
-      <c r="G13" s="79"/>
-      <c r="H13" s="79"/>
-      <c r="I13" s="80"/>
+      <c r="G13" s="45"/>
+      <c r="H13" s="45"/>
+      <c r="I13" s="46"/>
       <c r="J13" s="33"/>
-      <c r="K13" s="78"/>
-      <c r="L13" s="78"/>
-      <c r="M13" s="78"/>
+      <c r="K13" s="63"/>
+      <c r="L13" s="63"/>
+      <c r="M13" s="63"/>
       <c r="N13" s="33"/>
     </row>
     <row r="14" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="37"/>
-      <c r="C14" s="84"/>
-      <c r="D14" s="85"/>
-      <c r="E14" s="86"/>
+      <c r="C14" s="42"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="44"/>
       <c r="F14" s="26"/>
-      <c r="G14" s="84"/>
-      <c r="H14" s="85"/>
-      <c r="I14" s="85"/>
+      <c r="G14" s="42"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="43"/>
       <c r="J14" s="33"/>
-      <c r="K14" s="93"/>
-      <c r="L14" s="93"/>
-      <c r="M14" s="93"/>
+      <c r="K14" s="53"/>
+      <c r="L14" s="53"/>
+      <c r="M14" s="53"/>
       <c r="N14" s="35"/>
     </row>
     <row r="15" spans="1:15" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
       <c r="B15" s="38"/>
-      <c r="C15" s="84"/>
-      <c r="D15" s="85"/>
-      <c r="E15" s="86"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="44"/>
       <c r="F15" s="26"/>
-      <c r="G15" s="79"/>
-      <c r="H15" s="79"/>
-      <c r="I15" s="80"/>
+      <c r="G15" s="45"/>
+      <c r="H15" s="45"/>
+      <c r="I15" s="46"/>
       <c r="J15" s="33"/>
-      <c r="K15" s="87"/>
-      <c r="L15" s="87"/>
-      <c r="M15" s="87"/>
+      <c r="K15" s="47"/>
+      <c r="L15" s="47"/>
+      <c r="M15" s="47"/>
       <c r="N15" s="35"/>
     </row>
     <row r="16" spans="1:15" s="7" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
@@ -1543,266 +1540,266 @@
       <c r="N17"/>
     </row>
     <row r="18" spans="2:14" s="7" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="39" t="s">
+      <c r="B18" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="C18" s="39" t="s">
+      <c r="C18" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="D18" s="39"/>
-      <c r="E18" s="39"/>
-      <c r="F18" s="39"/>
-      <c r="G18" s="39"/>
+      <c r="D18" s="61"/>
+      <c r="E18" s="61"/>
+      <c r="F18" s="61"/>
+      <c r="G18" s="61"/>
       <c r="H18" s="25"/>
-      <c r="I18" s="39" t="s">
+      <c r="I18" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="J18" s="39" t="s">
+      <c r="J18" s="61" t="s">
         <v>11</v>
       </c>
       <c r="K18" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="L18" s="39" t="s">
+      <c r="L18" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="M18" s="75" t="s">
+      <c r="M18" s="59" t="s">
         <v>12</v>
       </c>
-      <c r="N18" s="75"/>
+      <c r="N18" s="59"/>
     </row>
     <row r="19" spans="2:14" s="7" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="40"/>
-      <c r="C19" s="40"/>
-      <c r="D19" s="40"/>
-      <c r="E19" s="40"/>
-      <c r="F19" s="40"/>
-      <c r="G19" s="40"/>
+      <c r="B19" s="54"/>
+      <c r="C19" s="54"/>
+      <c r="D19" s="54"/>
+      <c r="E19" s="54"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="54"/>
       <c r="H19" s="25"/>
-      <c r="I19" s="40"/>
-      <c r="J19" s="40"/>
+      <c r="I19" s="54"/>
+      <c r="J19" s="54"/>
       <c r="K19" s="31">
         <v>65</v>
       </c>
-      <c r="L19" s="40"/>
-      <c r="M19" s="76"/>
-      <c r="N19" s="76"/>
+      <c r="L19" s="54"/>
+      <c r="M19" s="60"/>
+      <c r="N19" s="60"/>
     </row>
     <row r="20" spans="2:14" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="28"/>
-      <c r="C20" s="41"/>
-      <c r="D20" s="41"/>
-      <c r="E20" s="41"/>
-      <c r="F20" s="41"/>
-      <c r="G20" s="41"/>
-      <c r="H20" s="41"/>
+      <c r="C20" s="93"/>
+      <c r="D20" s="93"/>
+      <c r="E20" s="93"/>
+      <c r="F20" s="93"/>
+      <c r="G20" s="93"/>
+      <c r="H20" s="93"/>
       <c r="I20" s="21"/>
       <c r="J20" s="21"/>
       <c r="K20" s="23"/>
       <c r="L20" s="23"/>
-      <c r="M20" s="42"/>
-      <c r="N20" s="42"/>
+      <c r="M20" s="94"/>
+      <c r="N20" s="94"/>
     </row>
     <row r="21" spans="2:14" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="28"/>
-      <c r="C21" s="41"/>
-      <c r="D21" s="41"/>
-      <c r="E21" s="41"/>
-      <c r="F21" s="41"/>
-      <c r="G21" s="41"/>
-      <c r="H21" s="41"/>
+      <c r="C21" s="93"/>
+      <c r="D21" s="93"/>
+      <c r="E21" s="93"/>
+      <c r="F21" s="93"/>
+      <c r="G21" s="93"/>
+      <c r="H21" s="93"/>
       <c r="I21" s="21"/>
       <c r="J21" s="21"/>
       <c r="K21" s="23"/>
       <c r="L21" s="23"/>
-      <c r="M21" s="42"/>
-      <c r="N21" s="42"/>
+      <c r="M21" s="94"/>
+      <c r="N21" s="94"/>
     </row>
     <row r="22" spans="2:14" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="28"/>
-      <c r="C22" s="41"/>
-      <c r="D22" s="41"/>
-      <c r="E22" s="41"/>
-      <c r="F22" s="41"/>
-      <c r="G22" s="41"/>
-      <c r="H22" s="41"/>
+      <c r="C22" s="93"/>
+      <c r="D22" s="93"/>
+      <c r="E22" s="93"/>
+      <c r="F22" s="93"/>
+      <c r="G22" s="93"/>
+      <c r="H22" s="93"/>
       <c r="I22" s="21"/>
       <c r="J22" s="21"/>
       <c r="K22" s="23"/>
       <c r="L22" s="23"/>
-      <c r="M22" s="42"/>
-      <c r="N22" s="42"/>
+      <c r="M22" s="94"/>
+      <c r="N22" s="94"/>
     </row>
     <row r="23" spans="2:14" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="28"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="41"/>
-      <c r="F23" s="41"/>
-      <c r="G23" s="41"/>
-      <c r="H23" s="41"/>
+      <c r="C23" s="93"/>
+      <c r="D23" s="93"/>
+      <c r="E23" s="93"/>
+      <c r="F23" s="93"/>
+      <c r="G23" s="93"/>
+      <c r="H23" s="93"/>
       <c r="I23" s="21"/>
       <c r="J23" s="21"/>
       <c r="K23" s="23"/>
       <c r="L23" s="23"/>
-      <c r="M23" s="42"/>
-      <c r="N23" s="42"/>
+      <c r="M23" s="94"/>
+      <c r="N23" s="94"/>
     </row>
     <row r="24" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="25" spans="2:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="26" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="40" t="s">
+      <c r="B26" s="54" t="s">
         <v>16</v>
       </c>
-      <c r="C26" s="40"/>
-      <c r="D26" s="40"/>
-      <c r="E26" s="40"/>
-      <c r="F26" s="40"/>
-      <c r="G26" s="40"/>
+      <c r="C26" s="54"/>
+      <c r="D26" s="54"/>
+      <c r="E26" s="54"/>
+      <c r="F26" s="54"/>
+      <c r="G26" s="54"/>
       <c r="H26" s="20"/>
-      <c r="K26" s="39" t="s">
+      <c r="K26" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="L26" s="39"/>
+      <c r="L26" s="61"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B27" s="56" t="s">
+      <c r="B27" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="C27" s="56"/>
+      <c r="C27" s="77"/>
       <c r="D27" s="13"/>
-      <c r="E27" s="58" t="s">
+      <c r="E27" s="79" t="s">
         <v>23</v>
       </c>
-      <c r="F27" s="58"/>
-      <c r="G27" s="58"/>
+      <c r="F27" s="79"/>
+      <c r="G27" s="79"/>
       <c r="H27" s="17"/>
-      <c r="K27" s="50" t="s">
+      <c r="K27" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="L27" s="53">
+      <c r="L27" s="74">
         <f>SUM(L20:L20)</f>
         <v>0</v>
       </c>
       <c r="N27" s="24"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B28" s="57"/>
-      <c r="C28" s="57"/>
+      <c r="B28" s="78"/>
+      <c r="C28" s="78"/>
       <c r="D28" s="14"/>
-      <c r="E28" s="59"/>
-      <c r="F28" s="59"/>
-      <c r="G28" s="59"/>
+      <c r="E28" s="80"/>
+      <c r="F28" s="80"/>
+      <c r="G28" s="80"/>
       <c r="H28" s="17"/>
-      <c r="K28" s="51"/>
-      <c r="L28" s="54"/>
+      <c r="K28" s="72"/>
+      <c r="L28" s="75"/>
     </row>
     <row r="29" spans="2:14" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="60" t="s">
+      <c r="B29" s="81" t="s">
         <v>17</v>
       </c>
-      <c r="C29" s="61"/>
+      <c r="C29" s="82"/>
       <c r="D29" s="13"/>
-      <c r="E29" s="62" t="s">
+      <c r="E29" s="83" t="s">
+        <v>23</v>
+      </c>
+      <c r="F29" s="79"/>
+      <c r="G29" s="79"/>
+      <c r="H29" s="18"/>
+      <c r="K29" s="73"/>
+      <c r="L29" s="76"/>
+    </row>
+    <row r="30" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B30" s="81"/>
+      <c r="C30" s="82"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="80"/>
+      <c r="F30" s="80"/>
+      <c r="G30" s="80"/>
+      <c r="H30" s="18"/>
+      <c r="K30" s="71" t="s">
+        <v>8</v>
+      </c>
+      <c r="L30" s="84"/>
+    </row>
+    <row r="31" spans="2:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B31" s="77" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="77"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="91" t="s">
+        <v>23</v>
+      </c>
+      <c r="F31" s="91"/>
+      <c r="G31" s="91"/>
+      <c r="H31" s="8"/>
+      <c r="K31" s="72"/>
+      <c r="L31" s="85"/>
+    </row>
+    <row r="32" spans="2:14" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="78"/>
+      <c r="C32" s="78"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="92"/>
+      <c r="F32" s="92"/>
+      <c r="G32" s="92"/>
+      <c r="H32" s="8"/>
+      <c r="K32" s="73"/>
+      <c r="L32" s="86"/>
+    </row>
+    <row r="33" spans="2:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B33" s="87" t="s">
         <v>25</v>
       </c>
-      <c r="F29" s="58"/>
-      <c r="G29" s="58"/>
-      <c r="H29" s="18"/>
-      <c r="K29" s="52"/>
-      <c r="L29" s="55"/>
-    </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B30" s="60"/>
-      <c r="C30" s="61"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="59"/>
-      <c r="F30" s="59"/>
-      <c r="G30" s="59"/>
-      <c r="H30" s="18"/>
-      <c r="K30" s="50" t="s">
-        <v>8</v>
-      </c>
-      <c r="L30" s="63"/>
-    </row>
-    <row r="31" spans="2:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="56" t="s">
-        <v>18</v>
-      </c>
-      <c r="C31" s="56"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="70" t="s">
-        <v>23</v>
-      </c>
-      <c r="F31" s="70"/>
-      <c r="G31" s="70"/>
-      <c r="H31" s="8"/>
-      <c r="K31" s="51"/>
-      <c r="L31" s="64"/>
-    </row>
-    <row r="32" spans="2:14" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="57"/>
-      <c r="C32" s="57"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="71"/>
-      <c r="F32" s="71"/>
-      <c r="G32" s="71"/>
-      <c r="H32" s="8"/>
-      <c r="K32" s="52"/>
-      <c r="L32" s="65"/>
-    </row>
-    <row r="33" spans="2:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="66" t="s">
-        <v>26</v>
-      </c>
-      <c r="C33" s="66"/>
+      <c r="C33" s="87"/>
       <c r="D33" s="16"/>
-      <c r="E33" s="68" t="s">
+      <c r="E33" s="89" t="s">
         <v>22</v>
       </c>
-      <c r="F33" s="68"/>
-      <c r="G33" s="68"/>
+      <c r="F33" s="89"/>
+      <c r="G33" s="89"/>
       <c r="H33" s="8"/>
-      <c r="K33" s="50" t="s">
+      <c r="K33" s="71" t="s">
         <v>20</v>
       </c>
-      <c r="L33" s="63">
+      <c r="L33" s="84">
         <f>L27</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:14" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="67"/>
-      <c r="C34" s="67"/>
+      <c r="B34" s="88"/>
+      <c r="C34" s="88"/>
       <c r="D34" s="15"/>
-      <c r="E34" s="69"/>
-      <c r="F34" s="69"/>
-      <c r="G34" s="69"/>
+      <c r="E34" s="90"/>
+      <c r="F34" s="90"/>
+      <c r="G34" s="90"/>
       <c r="H34" s="8"/>
-      <c r="K34" s="51"/>
-      <c r="L34" s="64"/>
+      <c r="K34" s="72"/>
+      <c r="L34" s="85"/>
     </row>
     <row r="35" spans="2:14" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="44" t="s">
-        <v>27</v>
-      </c>
-      <c r="C35" s="45"/>
-      <c r="D35" s="45"/>
-      <c r="E35" s="45"/>
-      <c r="F35" s="45"/>
-      <c r="G35" s="46"/>
+      <c r="B35" s="65" t="s">
+        <v>26</v>
+      </c>
+      <c r="C35" s="66"/>
+      <c r="D35" s="66"/>
+      <c r="E35" s="66"/>
+      <c r="F35" s="66"/>
+      <c r="G35" s="67"/>
       <c r="H35" s="19"/>
       <c r="J35" s="11"/>
-      <c r="K35" s="52"/>
-      <c r="L35" s="65"/>
+      <c r="K35" s="73"/>
+      <c r="L35" s="86"/>
     </row>
     <row r="36" spans="2:14" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="47"/>
-      <c r="C36" s="48"/>
-      <c r="D36" s="48"/>
-      <c r="E36" s="48"/>
-      <c r="F36" s="48"/>
-      <c r="G36" s="49"/>
+      <c r="B36" s="68"/>
+      <c r="C36" s="69"/>
+      <c r="D36" s="69"/>
+      <c r="E36" s="69"/>
+      <c r="F36" s="69"/>
+      <c r="G36" s="70"/>
       <c r="H36" s="19"/>
       <c r="K36" s="12"/>
       <c r="L36" s="12"/>
@@ -1860,15 +1857,53 @@
     <row r="46" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="47" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="49" spans="9:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="I49" s="43" t="s">
-        <v>28</v>
-      </c>
-      <c r="J49" s="43"/>
-      <c r="K49" s="43"/>
-      <c r="L49" s="43"/>
+      <c r="I49" s="64" t="s">
+        <v>27</v>
+      </c>
+      <c r="J49" s="64"/>
+      <c r="K49" s="64"/>
+      <c r="L49" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="54">
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="B26:G26"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C20:H20"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="C23:H23"/>
+    <mergeCell ref="M23:N23"/>
+    <mergeCell ref="C21:H21"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="C22:H22"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="I49:L49"/>
+    <mergeCell ref="B35:G36"/>
+    <mergeCell ref="K27:K29"/>
+    <mergeCell ref="L27:L29"/>
+    <mergeCell ref="B27:C28"/>
+    <mergeCell ref="E27:G28"/>
+    <mergeCell ref="B29:C30"/>
+    <mergeCell ref="E29:G30"/>
+    <mergeCell ref="L30:L32"/>
+    <mergeCell ref="K30:K32"/>
+    <mergeCell ref="K33:K35"/>
+    <mergeCell ref="L33:L35"/>
+    <mergeCell ref="B33:C34"/>
+    <mergeCell ref="E33:G34"/>
+    <mergeCell ref="B31:C32"/>
+    <mergeCell ref="E31:G32"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="M18:N19"/>
+    <mergeCell ref="L18:L19"/>
+    <mergeCell ref="C18:G19"/>
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="J18:J19"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="K13:M13"/>
+    <mergeCell ref="G13:I13"/>
     <mergeCell ref="K1:N2"/>
     <mergeCell ref="L4:N5"/>
     <mergeCell ref="C15:E15"/>
@@ -1885,44 +1920,6 @@
     <mergeCell ref="C13:E13"/>
     <mergeCell ref="L6:N7"/>
     <mergeCell ref="L8:N9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="M18:N19"/>
-    <mergeCell ref="L18:L19"/>
-    <mergeCell ref="C18:G19"/>
-    <mergeCell ref="I18:I19"/>
-    <mergeCell ref="J18:J19"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="K13:M13"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="I49:L49"/>
-    <mergeCell ref="B35:G36"/>
-    <mergeCell ref="K27:K29"/>
-    <mergeCell ref="L27:L29"/>
-    <mergeCell ref="B27:C28"/>
-    <mergeCell ref="E27:G28"/>
-    <mergeCell ref="B29:C30"/>
-    <mergeCell ref="E29:G30"/>
-    <mergeCell ref="L30:L32"/>
-    <mergeCell ref="K30:K32"/>
-    <mergeCell ref="K33:K35"/>
-    <mergeCell ref="L33:L35"/>
-    <mergeCell ref="B33:C34"/>
-    <mergeCell ref="E33:G34"/>
-    <mergeCell ref="B31:C32"/>
-    <mergeCell ref="E31:G32"/>
-    <mergeCell ref="K26:L26"/>
-    <mergeCell ref="B26:G26"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C20:H20"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="C23:H23"/>
-    <mergeCell ref="M23:N23"/>
-    <mergeCell ref="C21:H21"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="C22:H22"/>
-    <mergeCell ref="M22:N22"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="F13:F15">
@@ -1950,13 +1947,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a52bf194-6401-462b-9261-416d3ab8d515">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2189,20 +2185,19 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a52bf194-6401-462b-9261-416d3ab8d515">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B752BE4-1396-4BCB-B02F-A8A256B5B09D}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B73DC9C3-8993-467B-9C7F-6F901699B4B8}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="a52bf194-6401-462b-9261-416d3ab8d515"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2227,9 +2222,11 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B73DC9C3-8993-467B-9C7F-6F901699B4B8}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B752BE4-1396-4BCB-B02F-A8A256B5B09D}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="a52bf194-6401-462b-9261-416d3ab8d515"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/utils/po_templates/po_template.xlsx
+++ b/utils/po_templates/po_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbolanos\Desktop\projects\cps-tool\utils\po_templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{035B9021-658B-4CBC-89F6-481794FB1178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4E70091-4945-405E-B2CC-5DCF34F1FD55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,6 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$N$51</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -716,6 +715,132 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -732,12 +857,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -761,128 +880,8 @@
     <xf numFmtId="0" fontId="9" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1293,12 +1292,12 @@
       <c r="H1" s="6"/>
       <c r="I1" s="6"/>
       <c r="J1" s="6"/>
-      <c r="K1" s="39" t="s">
+      <c r="K1" s="81" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="39"/>
-      <c r="M1" s="39"/>
-      <c r="N1" s="39"/>
+      <c r="L1" s="81"/>
+      <c r="M1" s="81"/>
+      <c r="N1" s="81"/>
     </row>
     <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E2" s="6"/>
@@ -1307,10 +1306,10 @@
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
       <c r="J2" s="6"/>
-      <c r="K2" s="39"/>
-      <c r="L2" s="39"/>
-      <c r="M2" s="39"/>
-      <c r="N2" s="39"/>
+      <c r="K2" s="81"/>
+      <c r="L2" s="81"/>
+      <c r="M2" s="81"/>
+      <c r="N2" s="81"/>
     </row>
     <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E3" s="6"/>
@@ -1326,88 +1325,88 @@
       <c r="O3" s="6"/>
     </row>
     <row r="4" spans="1:15" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="K4" s="50" t="s">
+      <c r="K4" s="90" t="s">
         <v>0</v>
       </c>
-      <c r="L4" s="40"/>
-      <c r="M4" s="40"/>
-      <c r="N4" s="40"/>
+      <c r="L4" s="82"/>
+      <c r="M4" s="82"/>
+      <c r="N4" s="82"/>
     </row>
     <row r="5" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="54" t="s">
+      <c r="B5" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="54"/>
+      <c r="C5" s="40"/>
       <c r="D5" s="20"/>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
       <c r="I5" s="10"/>
-      <c r="K5" s="49"/>
-      <c r="L5" s="41"/>
-      <c r="M5" s="41"/>
-      <c r="N5" s="41"/>
+      <c r="K5" s="89"/>
+      <c r="L5" s="83"/>
+      <c r="M5" s="83"/>
+      <c r="N5" s="83"/>
     </row>
     <row r="6" spans="1:15" s="1" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="51"/>
-      <c r="C6" s="51"/>
+      <c r="B6" s="91"/>
+      <c r="C6" s="91"/>
       <c r="D6" s="29"/>
       <c r="E6" s="30"/>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
       <c r="H6" s="7"/>
       <c r="I6" s="4"/>
-      <c r="K6" s="48" t="s">
+      <c r="K6" s="88" t="s">
         <v>15</v>
       </c>
-      <c r="L6" s="55"/>
-      <c r="M6" s="55"/>
-      <c r="N6" s="55"/>
+      <c r="L6" s="94"/>
+      <c r="M6" s="94"/>
+      <c r="N6" s="94"/>
     </row>
     <row r="7" spans="1:15" s="1" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="52"/>
-      <c r="C7" s="52"/>
+      <c r="B7" s="92"/>
+      <c r="C7" s="92"/>
       <c r="D7" s="29"/>
       <c r="E7" s="30"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
       <c r="I7" s="4"/>
-      <c r="K7" s="49"/>
-      <c r="L7" s="41"/>
-      <c r="M7" s="41"/>
-      <c r="N7" s="41"/>
+      <c r="K7" s="89"/>
+      <c r="L7" s="83"/>
+      <c r="M7" s="83"/>
+      <c r="N7" s="83"/>
     </row>
     <row r="8" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="52"/>
-      <c r="C8" s="52"/>
+      <c r="B8" s="92"/>
+      <c r="C8" s="92"/>
       <c r="D8" s="29"/>
       <c r="E8" s="30"/>
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
       <c r="I8" s="4"/>
-      <c r="K8" s="56" t="s">
+      <c r="K8" s="72" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="55"/>
-      <c r="M8" s="55"/>
-      <c r="N8" s="55"/>
+      <c r="L8" s="94"/>
+      <c r="M8" s="94"/>
+      <c r="N8" s="94"/>
     </row>
     <row r="9" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="52"/>
-      <c r="C9" s="52"/>
+      <c r="B9" s="92"/>
+      <c r="C9" s="92"/>
       <c r="D9" s="29"/>
       <c r="E9" s="30"/>
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
       <c r="I9" s="4"/>
-      <c r="K9" s="56"/>
-      <c r="L9" s="41"/>
-      <c r="M9" s="41"/>
-      <c r="N9" s="41"/>
+      <c r="K9" s="72"/>
+      <c r="L9" s="83"/>
+      <c r="M9" s="83"/>
+      <c r="N9" s="83"/>
     </row>
     <row r="10" spans="1:15" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="7"/>
@@ -1438,75 +1437,75 @@
       <c r="B12" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="57" t="s">
+      <c r="C12" s="73" t="s">
         <v>2</v>
       </c>
-      <c r="D12" s="58"/>
-      <c r="E12" s="58"/>
+      <c r="D12" s="74"/>
+      <c r="E12" s="74"/>
       <c r="F12" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="G12" s="62" t="s">
+      <c r="G12" s="77" t="s">
         <v>2</v>
       </c>
-      <c r="H12" s="58"/>
-      <c r="I12" s="58"/>
+      <c r="H12" s="74"/>
+      <c r="I12" s="74"/>
       <c r="J12" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="K12" s="62" t="s">
+      <c r="K12" s="77" t="s">
         <v>2</v>
       </c>
-      <c r="L12" s="58"/>
-      <c r="M12" s="58"/>
+      <c r="L12" s="74"/>
+      <c r="M12" s="74"/>
       <c r="N12" s="34" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="36"/>
-      <c r="C13" s="42"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="44"/>
+      <c r="C13" s="84"/>
+      <c r="D13" s="85"/>
+      <c r="E13" s="86"/>
       <c r="F13" s="26"/>
-      <c r="G13" s="45"/>
-      <c r="H13" s="45"/>
-      <c r="I13" s="46"/>
+      <c r="G13" s="79"/>
+      <c r="H13" s="79"/>
+      <c r="I13" s="80"/>
       <c r="J13" s="33"/>
-      <c r="K13" s="63"/>
-      <c r="L13" s="63"/>
-      <c r="M13" s="63"/>
+      <c r="K13" s="78"/>
+      <c r="L13" s="78"/>
+      <c r="M13" s="78"/>
       <c r="N13" s="33"/>
     </row>
     <row r="14" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="37"/>
-      <c r="C14" s="42"/>
-      <c r="D14" s="43"/>
-      <c r="E14" s="44"/>
+      <c r="C14" s="84"/>
+      <c r="D14" s="85"/>
+      <c r="E14" s="86"/>
       <c r="F14" s="26"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="43"/>
-      <c r="I14" s="43"/>
+      <c r="G14" s="84"/>
+      <c r="H14" s="85"/>
+      <c r="I14" s="85"/>
       <c r="J14" s="33"/>
-      <c r="K14" s="53"/>
-      <c r="L14" s="53"/>
-      <c r="M14" s="53"/>
+      <c r="K14" s="93"/>
+      <c r="L14" s="93"/>
+      <c r="M14" s="93"/>
       <c r="N14" s="35"/>
     </row>
     <row r="15" spans="1:15" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
       <c r="B15" s="38"/>
-      <c r="C15" s="42"/>
-      <c r="D15" s="43"/>
-      <c r="E15" s="44"/>
+      <c r="C15" s="84"/>
+      <c r="D15" s="85"/>
+      <c r="E15" s="86"/>
       <c r="F15" s="26"/>
-      <c r="G15" s="45"/>
-      <c r="H15" s="45"/>
-      <c r="I15" s="46"/>
+      <c r="G15" s="79"/>
+      <c r="H15" s="79"/>
+      <c r="I15" s="80"/>
       <c r="J15" s="33"/>
-      <c r="K15" s="47"/>
-      <c r="L15" s="47"/>
-      <c r="M15" s="47"/>
+      <c r="K15" s="87"/>
+      <c r="L15" s="87"/>
+      <c r="M15" s="87"/>
       <c r="N15" s="35"/>
     </row>
     <row r="16" spans="1:15" s="7" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
@@ -1540,266 +1539,266 @@
       <c r="N17"/>
     </row>
     <row r="18" spans="2:14" s="7" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="61" t="s">
+      <c r="B18" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="C18" s="61" t="s">
+      <c r="C18" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="D18" s="61"/>
-      <c r="E18" s="61"/>
-      <c r="F18" s="61"/>
-      <c r="G18" s="61"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="39"/>
       <c r="H18" s="25"/>
-      <c r="I18" s="61" t="s">
+      <c r="I18" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="J18" s="61" t="s">
+      <c r="J18" s="39" t="s">
         <v>11</v>
       </c>
       <c r="K18" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="L18" s="61" t="s">
+      <c r="L18" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="M18" s="59" t="s">
+      <c r="M18" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="N18" s="59"/>
+      <c r="N18" s="75"/>
     </row>
     <row r="19" spans="2:14" s="7" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="54"/>
-      <c r="C19" s="54"/>
-      <c r="D19" s="54"/>
-      <c r="E19" s="54"/>
-      <c r="F19" s="54"/>
-      <c r="G19" s="54"/>
+      <c r="B19" s="40"/>
+      <c r="C19" s="40"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="40"/>
+      <c r="F19" s="40"/>
+      <c r="G19" s="40"/>
       <c r="H19" s="25"/>
-      <c r="I19" s="54"/>
-      <c r="J19" s="54"/>
+      <c r="I19" s="40"/>
+      <c r="J19" s="40"/>
       <c r="K19" s="31">
         <v>65</v>
       </c>
-      <c r="L19" s="54"/>
-      <c r="M19" s="60"/>
-      <c r="N19" s="60"/>
+      <c r="L19" s="40"/>
+      <c r="M19" s="76"/>
+      <c r="N19" s="76"/>
     </row>
     <row r="20" spans="2:14" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="28"/>
-      <c r="C20" s="93"/>
-      <c r="D20" s="93"/>
-      <c r="E20" s="93"/>
-      <c r="F20" s="93"/>
-      <c r="G20" s="93"/>
-      <c r="H20" s="93"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="41"/>
       <c r="I20" s="21"/>
       <c r="J20" s="21"/>
       <c r="K20" s="23"/>
       <c r="L20" s="23"/>
-      <c r="M20" s="94"/>
-      <c r="N20" s="94"/>
+      <c r="M20" s="42"/>
+      <c r="N20" s="42"/>
     </row>
     <row r="21" spans="2:14" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="28"/>
-      <c r="C21" s="93"/>
-      <c r="D21" s="93"/>
-      <c r="E21" s="93"/>
-      <c r="F21" s="93"/>
-      <c r="G21" s="93"/>
-      <c r="H21" s="93"/>
+      <c r="C21" s="41"/>
+      <c r="D21" s="41"/>
+      <c r="E21" s="41"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="41"/>
+      <c r="H21" s="41"/>
       <c r="I21" s="21"/>
       <c r="J21" s="21"/>
       <c r="K21" s="23"/>
       <c r="L21" s="23"/>
-      <c r="M21" s="94"/>
-      <c r="N21" s="94"/>
+      <c r="M21" s="42"/>
+      <c r="N21" s="42"/>
     </row>
     <row r="22" spans="2:14" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="28"/>
-      <c r="C22" s="93"/>
-      <c r="D22" s="93"/>
-      <c r="E22" s="93"/>
-      <c r="F22" s="93"/>
-      <c r="G22" s="93"/>
-      <c r="H22" s="93"/>
+      <c r="C22" s="41"/>
+      <c r="D22" s="41"/>
+      <c r="E22" s="41"/>
+      <c r="F22" s="41"/>
+      <c r="G22" s="41"/>
+      <c r="H22" s="41"/>
       <c r="I22" s="21"/>
       <c r="J22" s="21"/>
       <c r="K22" s="23"/>
       <c r="L22" s="23"/>
-      <c r="M22" s="94"/>
-      <c r="N22" s="94"/>
+      <c r="M22" s="42"/>
+      <c r="N22" s="42"/>
     </row>
     <row r="23" spans="2:14" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="28"/>
-      <c r="C23" s="93"/>
-      <c r="D23" s="93"/>
-      <c r="E23" s="93"/>
-      <c r="F23" s="93"/>
-      <c r="G23" s="93"/>
-      <c r="H23" s="93"/>
+      <c r="C23" s="41"/>
+      <c r="D23" s="41"/>
+      <c r="E23" s="41"/>
+      <c r="F23" s="41"/>
+      <c r="G23" s="41"/>
+      <c r="H23" s="41"/>
       <c r="I23" s="21"/>
       <c r="J23" s="21"/>
       <c r="K23" s="23"/>
       <c r="L23" s="23"/>
-      <c r="M23" s="94"/>
-      <c r="N23" s="94"/>
+      <c r="M23" s="42"/>
+      <c r="N23" s="42"/>
     </row>
     <row r="24" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="25" spans="2:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="26" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="54" t="s">
+      <c r="B26" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="C26" s="54"/>
-      <c r="D26" s="54"/>
-      <c r="E26" s="54"/>
-      <c r="F26" s="54"/>
-      <c r="G26" s="54"/>
+      <c r="C26" s="40"/>
+      <c r="D26" s="40"/>
+      <c r="E26" s="40"/>
+      <c r="F26" s="40"/>
+      <c r="G26" s="40"/>
       <c r="H26" s="20"/>
-      <c r="K26" s="61" t="s">
+      <c r="K26" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="L26" s="61"/>
+      <c r="L26" s="39"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B27" s="77" t="s">
+      <c r="B27" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="C27" s="77"/>
+      <c r="C27" s="56"/>
       <c r="D27" s="13"/>
-      <c r="E27" s="79" t="s">
+      <c r="E27" s="58" t="s">
         <v>23</v>
       </c>
-      <c r="F27" s="79"/>
-      <c r="G27" s="79"/>
+      <c r="F27" s="58"/>
+      <c r="G27" s="58"/>
       <c r="H27" s="17"/>
-      <c r="K27" s="71" t="s">
+      <c r="K27" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="L27" s="74">
+      <c r="L27" s="53">
         <f>SUM(L20:L20)</f>
         <v>0</v>
       </c>
       <c r="N27" s="24"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B28" s="78"/>
-      <c r="C28" s="78"/>
+      <c r="B28" s="57"/>
+      <c r="C28" s="57"/>
       <c r="D28" s="14"/>
-      <c r="E28" s="80"/>
-      <c r="F28" s="80"/>
-      <c r="G28" s="80"/>
+      <c r="E28" s="59"/>
+      <c r="F28" s="59"/>
+      <c r="G28" s="59"/>
       <c r="H28" s="17"/>
-      <c r="K28" s="72"/>
-      <c r="L28" s="75"/>
+      <c r="K28" s="51"/>
+      <c r="L28" s="54"/>
     </row>
     <row r="29" spans="2:14" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="81" t="s">
+      <c r="B29" s="60" t="s">
         <v>17</v>
       </c>
-      <c r="C29" s="82"/>
+      <c r="C29" s="61"/>
       <c r="D29" s="13"/>
-      <c r="E29" s="83" t="s">
+      <c r="E29" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="F29" s="79"/>
-      <c r="G29" s="79"/>
+      <c r="F29" s="58"/>
+      <c r="G29" s="58"/>
       <c r="H29" s="18"/>
-      <c r="K29" s="73"/>
-      <c r="L29" s="76"/>
+      <c r="K29" s="52"/>
+      <c r="L29" s="55"/>
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B30" s="81"/>
-      <c r="C30" s="82"/>
+      <c r="B30" s="60"/>
+      <c r="C30" s="61"/>
       <c r="D30" s="14"/>
-      <c r="E30" s="80"/>
-      <c r="F30" s="80"/>
-      <c r="G30" s="80"/>
+      <c r="E30" s="59"/>
+      <c r="F30" s="59"/>
+      <c r="G30" s="59"/>
       <c r="H30" s="18"/>
-      <c r="K30" s="71" t="s">
+      <c r="K30" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="L30" s="84"/>
+      <c r="L30" s="63"/>
     </row>
     <row r="31" spans="2:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="77" t="s">
+      <c r="B31" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="C31" s="77"/>
+      <c r="C31" s="56"/>
       <c r="D31" s="13"/>
-      <c r="E31" s="91" t="s">
+      <c r="E31" s="70" t="s">
         <v>23</v>
       </c>
-      <c r="F31" s="91"/>
-      <c r="G31" s="91"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="70"/>
       <c r="H31" s="8"/>
-      <c r="K31" s="72"/>
-      <c r="L31" s="85"/>
+      <c r="K31" s="51"/>
+      <c r="L31" s="64"/>
     </row>
     <row r="32" spans="2:14" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="78"/>
-      <c r="C32" s="78"/>
+      <c r="B32" s="57"/>
+      <c r="C32" s="57"/>
       <c r="D32" s="14"/>
-      <c r="E32" s="92"/>
-      <c r="F32" s="92"/>
-      <c r="G32" s="92"/>
+      <c r="E32" s="71"/>
+      <c r="F32" s="71"/>
+      <c r="G32" s="71"/>
       <c r="H32" s="8"/>
-      <c r="K32" s="73"/>
-      <c r="L32" s="86"/>
+      <c r="K32" s="52"/>
+      <c r="L32" s="65"/>
     </row>
     <row r="33" spans="2:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="87" t="s">
+      <c r="B33" s="66" t="s">
         <v>25</v>
       </c>
-      <c r="C33" s="87"/>
+      <c r="C33" s="66"/>
       <c r="D33" s="16"/>
-      <c r="E33" s="89" t="s">
+      <c r="E33" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="F33" s="89"/>
-      <c r="G33" s="89"/>
+      <c r="F33" s="68"/>
+      <c r="G33" s="68"/>
       <c r="H33" s="8"/>
-      <c r="K33" s="71" t="s">
+      <c r="K33" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="L33" s="84">
+      <c r="L33" s="63">
         <f>L27</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:14" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="88"/>
-      <c r="C34" s="88"/>
+      <c r="B34" s="67"/>
+      <c r="C34" s="67"/>
       <c r="D34" s="15"/>
-      <c r="E34" s="90"/>
-      <c r="F34" s="90"/>
-      <c r="G34" s="90"/>
+      <c r="E34" s="69"/>
+      <c r="F34" s="69"/>
+      <c r="G34" s="69"/>
       <c r="H34" s="8"/>
-      <c r="K34" s="72"/>
-      <c r="L34" s="85"/>
+      <c r="K34" s="51"/>
+      <c r="L34" s="64"/>
     </row>
     <row r="35" spans="2:14" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="65" t="s">
+      <c r="B35" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="C35" s="66"/>
-      <c r="D35" s="66"/>
-      <c r="E35" s="66"/>
-      <c r="F35" s="66"/>
-      <c r="G35" s="67"/>
+      <c r="C35" s="45"/>
+      <c r="D35" s="45"/>
+      <c r="E35" s="45"/>
+      <c r="F35" s="45"/>
+      <c r="G35" s="46"/>
       <c r="H35" s="19"/>
       <c r="J35" s="11"/>
-      <c r="K35" s="73"/>
-      <c r="L35" s="86"/>
+      <c r="K35" s="52"/>
+      <c r="L35" s="65"/>
     </row>
     <row r="36" spans="2:14" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="68"/>
-      <c r="C36" s="69"/>
-      <c r="D36" s="69"/>
-      <c r="E36" s="69"/>
-      <c r="F36" s="69"/>
-      <c r="G36" s="70"/>
+      <c r="B36" s="47"/>
+      <c r="C36" s="48"/>
+      <c r="D36" s="48"/>
+      <c r="E36" s="48"/>
+      <c r="F36" s="48"/>
+      <c r="G36" s="49"/>
       <c r="H36" s="19"/>
       <c r="K36" s="12"/>
       <c r="L36" s="12"/>
@@ -1857,26 +1856,42 @@
     <row r="46" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="47" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="49" spans="9:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="I49" s="64" t="s">
+      <c r="I49" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="J49" s="64"/>
-      <c r="K49" s="64"/>
-      <c r="L49" s="64"/>
+      <c r="J49" s="43"/>
+      <c r="K49" s="43"/>
+      <c r="L49" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="54">
-    <mergeCell ref="K26:L26"/>
-    <mergeCell ref="B26:G26"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C20:H20"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="C23:H23"/>
-    <mergeCell ref="M23:N23"/>
-    <mergeCell ref="C21:H21"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="C22:H22"/>
-    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="K1:N2"/>
+    <mergeCell ref="L4:N5"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="K15:M15"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C9"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="K14:M14"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="L6:N7"/>
+    <mergeCell ref="L8:N9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="M18:N19"/>
+    <mergeCell ref="L18:L19"/>
+    <mergeCell ref="C18:G19"/>
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="J18:J19"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="K13:M13"/>
+    <mergeCell ref="G13:I13"/>
     <mergeCell ref="I49:L49"/>
     <mergeCell ref="B35:G36"/>
     <mergeCell ref="K27:K29"/>
@@ -1893,33 +1908,17 @@
     <mergeCell ref="E33:G34"/>
     <mergeCell ref="B31:C32"/>
     <mergeCell ref="E31:G32"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="M18:N19"/>
-    <mergeCell ref="L18:L19"/>
-    <mergeCell ref="C18:G19"/>
-    <mergeCell ref="I18:I19"/>
-    <mergeCell ref="J18:J19"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="K13:M13"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="K1:N2"/>
-    <mergeCell ref="L4:N5"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="K15:M15"/>
-    <mergeCell ref="K6:K7"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C9"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="L6:N7"/>
-    <mergeCell ref="L8:N9"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="B26:G26"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C20:H20"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="C23:H23"/>
+    <mergeCell ref="M23:N23"/>
+    <mergeCell ref="C21:H21"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="C22:H22"/>
+    <mergeCell ref="M22:N22"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="F13:F15">
@@ -1937,7 +1936,7 @@
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="60" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="68" orientation="portrait" r:id="rId1"/>
   <headerFooter>
     <oddFooter>&amp;C_________________________________________________________________________________________
 CPS AFRICA NV - Bijkhoevelaan 12 - 2110 Wijnegem - VAT BE0578.970.135</oddFooter>
@@ -1947,12 +1946,13 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a52bf194-6401-462b-9261-416d3ab8d515">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2185,19 +2185,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a52bf194-6401-462b-9261-416d3ab8d515">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B73DC9C3-8993-467B-9C7F-6F901699B4B8}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B752BE4-1396-4BCB-B02F-A8A256B5B09D}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="a52bf194-6401-462b-9261-416d3ab8d515"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2222,11 +2223,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B752BE4-1396-4BCB-B02F-A8A256B5B09D}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B73DC9C3-8993-467B-9C7F-6F901699B4B8}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="a52bf194-6401-462b-9261-416d3ab8d515"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>